--- a/sampleprojects/TaxReturn/excel/states/OK.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/OK.xlsx
@@ -9,14 +9,15 @@
   <sheets>
     <sheet name="ok tax" sheetId="2" r:id="rId4"/>
     <sheet name="OK Military Retirement Exclusio" sheetId="3" r:id="rId6"/>
-    <sheet name="EDD" sheetId="4" r:id="rId7"/>
+    <sheet name="OK Tax Table" sheetId="4" r:id="rId7"/>
+    <sheet name="EDD" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
   <si>
     <t>DT: ok tax</t>
   </si>
@@ -42,42 +43,102 @@
     <t>DSL: INITIAL ACTIONS</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>set result.ok_limit_1 = ok_bracket_1_limit; set result.ok_limit_2 = ok_bracket_2_limit; set result.ok_limit_3 = ok_bracket_3_limit; set result.ok_limit_4 = ok_bracket_4_limit; set result.ok_limit_5 = ok_bracket_5_limit; set result.ok_high_base = ok_single_high_base; set result.ok_std_deduction = ok_standard_deduction_single; set result.ok_senior_limit = ok_senior_limit_single</t>
+  </si>
+  <si>
     <t>CONDITIONS: COMMENTS</t>
   </si>
   <si>
     <t>DSL: CONDITIONS</t>
   </si>
   <si>
-    <t>Married filing jointly</t>
-  </si>
-  <si>
-    <t>job.filing_status is equal to "MFJ"</t>
+    <t>Married Filing Joint or Qualifying Surviving Spouse</t>
+  </si>
+  <si>
+    <t>job.filing_status is equal to "MFJ" or job.filing_status is equal to "QSS"</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Head of household</t>
+    <t>Head of Household: joint table column, its own standard deduction</t>
   </si>
   <si>
     <t>job.filing_status is equal to "HOH"</t>
   </si>
   <si>
-    <t>Married filing separately</t>
+    <t>Married Filing Separate: single table column</t>
   </si>
   <si>
     <t>job.filing_status is equal to "MFS"</t>
   </si>
   <si>
+    <t>*</t>
+  </si>
+  <si>
     <t>ACTIONS: COMMENTS</t>
   </si>
   <si>
     <t>DSL: ACTIONS</t>
   </si>
   <si>
+    <t>Married filing joint or head of household table column</t>
+  </si>
+  <si>
+    <t>set result.ok_limit_1 = ok_joint_bracket_1_limit; set result.ok_limit_2 = ok_joint_bracket_2_limit; set result.ok_limit_3 = ok_joint_bracket_3_limit; set result.ok_limit_4 = ok_joint_bracket_4_limit; set result.ok_limit_5 = ok_joint_bracket_5_limit; set result.ok_high_base = ok_joint_high_base</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Line 10 $12,700</t>
+  </si>
+  <si>
+    <t>set result.ok_std_deduction = ok_standard_deduction_joint; set result.ok_senior_limit = ok_senior_limit_joint</t>
+  </si>
+  <si>
+    <t>Line 10 $9,350</t>
+  </si>
+  <si>
+    <t>set result.ok_std_deduction = ok_standard_deduction_hoh; set result.ok_senior_limit = ok_senior_limit_hoh</t>
+  </si>
+  <si>
+    <t>Line 10 $6,350</t>
+  </si>
+  <si>
+    <t>set result.ok_std_deduction = ok_standard_deduction_mfs; set result.ok_senior_limit = ok_senior_limit_mfs</t>
+  </si>
+  <si>
+    <t>Line 11 exemptions, with the special 65+ exemption under the AGI limit</t>
+  </si>
+  <si>
+    <t>set result.ok_exemptions = length of job.taxpayers + length of job.dependents; if result.state_calc_agi &lt;= result.ok_senior_limit then { set result.ok_exemptions = result.ok_exemptions + result.senior_std_count; } endif</t>
+  </si>
+  <si>
+    <t>Line 13 taxable income; line 14 tax from the table</t>
+  </si>
+  <si>
+    <t>set result.ok_taxable_income = the maximum of (result.state_calc_agi - result.ok_std_deduction - result.ok_exemptions * ok_personal_exemption_credit) and 0.0; perform OK_Tax_Table; set result.ok_tax = result.ok_table_tax</t>
+  </si>
+  <si>
+    <t>Harvested onto the roster by Compute_Roster_State_Tax</t>
+  </si>
+  <si>
+    <t>set result.computed_state_taxable_income = result.ok_taxable_income; set result.computed_state_tax = result.ok_tax</t>
+  </si>
+  <si>
+    <t>Audit</t>
+  </si>
+  <si>
+    <t>add "  Oklahoma (Form 511 2025): taxable income $" + result.ok_taxable_income + " (standard deduction $" + result.ok_std_deduction + ", " + result.ok_exemptions + " exemptions), tax $" + result.ok_tax to job.audit_trail</t>
+  </si>
+  <si>
     <t>DT: OK Military Retirement Exclusion</t>
   </si>
   <si>
@@ -93,6 +154,36 @@
     <t>set result.ok_military_retirement_exemption = 0</t>
   </si>
   <si>
+    <t>DT: OK Tax Table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMENTS: </t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 43610</t>
+  </si>
+  <si>
+    <t>set result.ok_band_midpoint = (the floor of (result.ok_taxable_income / 50.0)) * 50.0 + 25.0</t>
+  </si>
+  <si>
+    <t>Less than $100,000: the table</t>
+  </si>
+  <si>
+    <t>result.ok_taxable_income &lt; ok_table_limit</t>
+  </si>
+  <si>
+    <t>Bracket tax at the band midpoint, rounded</t>
+  </si>
+  <si>
+    <t>set result.ok_table_tax = the floor of (ok_bracket_1_rate * (the minimum of result.ok_band_midpoint and result.ok_limit_1) + ok_bracket_2_rate * (the maximum of ((the minimum of result.ok_band_midpoint and result.ok_limit_2) - result.ok_limit_1) and 0.0) + ok_bracket_3_rate * (the maximum of ((the minimum of result.ok_band_midpoint and result.ok_limit_3) - result.ok_limit_2) and 0.0) + ok_bracket_4_rate * (the maximum of ((the minimum of result.ok_band_midpoint and result.ok_limit_4) - result.ok_limit_3) and 0.0) + ok_bracket_5_rate * (the maximum of ((the minimum of result.ok_band_midpoint and result.ok_limit_5) - result.ok_limit_4) and 0.0) + ok_bracket_6_rate * (the maximum of (result.ok_band_midpoint - result.ok_limit_5) and 0.0) + 0.5)</t>
+  </si>
+  <si>
+    <t>Page 38: base plus 0.0475 over $100,000</t>
+  </si>
+  <si>
+    <t>set result.ok_table_tax = the floor of (result.ok_high_base + ok_bracket_6_rate * (result.ok_taxable_income - ok_table_limit) + 0.5)</t>
+  </si>
+  <si>
     <t>EDD: EDD</t>
   </si>
   <si>
@@ -138,15 +229,27 @@
     <t>result</t>
   </si>
   <si>
-    <t>(21 attributes)</t>
+    <t>(44 attributes)</t>
+  </si>
+  <si>
+    <t>ok_band_midpoint</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>OK tax computation (ok_tax)</t>
   </si>
   <si>
     <t>ok_base_tax</t>
   </si>
   <si>
-    <t>double</t>
-  </si>
-  <si>
     <t>0.0</t>
   </si>
   <si>
@@ -162,7 +265,7 @@
     <t>1000.0</t>
   </si>
   <si>
-    <t>OK tax bracket 1 upper limit (2025). Source: Oklahoma Tax Commission</t>
+    <t>OK 2025 Form 511 packet, Income Tax Table: Single/MFS 0.25% on the first $1,000</t>
   </si>
   <si>
     <t>ok_bracket_1_rate</t>
@@ -180,7 +283,7 @@
     <t>2500.0</t>
   </si>
   <si>
-    <t>OK tax bracket 2 upper limit (2025)</t>
+    <t>OK 2025 Form 511 packet, Income Tax Table: Single/MFS 0.75% to $2,500</t>
   </si>
   <si>
     <t>ok_bracket_2_rate</t>
@@ -198,7 +301,7 @@
     <t>3750.0</t>
   </si>
   <si>
-    <t>OK tax bracket 3 upper limit (2025)</t>
+    <t>OK 2025 Form 511 packet, Income Tax Table: Single/MFS 1.75% to $3,750</t>
   </si>
   <si>
     <t>ok_bracket_3_rate</t>
@@ -216,7 +319,7 @@
     <t>4900.0</t>
   </si>
   <si>
-    <t>OK tax bracket 4 upper limit (2025)</t>
+    <t>OK 2025 Form 511 packet, Income Tax Table: Single/MFS 2.75% to $4,900</t>
   </si>
   <si>
     <t>ok_bracket_4_rate</t>
@@ -234,7 +337,7 @@
     <t>7200.0</t>
   </si>
   <si>
-    <t>OK tax bracket 5 upper limit (2025)</t>
+    <t>OK 2025 Form 511 packet, Income Tax Table: Single/MFS 3.75% to $7,200; 4.75% over</t>
   </si>
   <si>
     <t>ok_bracket_5_rate</t>
@@ -261,6 +364,81 @@
     <t>OK total personal exemption credit (computed)</t>
   </si>
   <si>
+    <t>ok_exemptions</t>
+  </si>
+  <si>
+    <t>ok_high_base</t>
+  </si>
+  <si>
+    <t>ok_joint_bracket_1_limit</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>OK 2025 Form 511 packet, Income Tax Table: MFJ/HOH/QSS 0.25% on the first $2,000</t>
+  </si>
+  <si>
+    <t>ok_joint_bracket_2_limit</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>OK 2025 Form 511 packet, Income Tax Table: MFJ/HOH/QSS 0.75% to $5,000</t>
+  </si>
+  <si>
+    <t>ok_joint_bracket_3_limit</t>
+  </si>
+  <si>
+    <t>7500</t>
+  </si>
+  <si>
+    <t>OK 2025 Form 511 packet, Income Tax Table: MFJ/HOH/QSS 1.75% to $7,500</t>
+  </si>
+  <si>
+    <t>ok_joint_bracket_4_limit</t>
+  </si>
+  <si>
+    <t>9800</t>
+  </si>
+  <si>
+    <t>OK 2025 Form 511 packet, Income Tax Table: MFJ/HOH/QSS 2.75% to $9,800</t>
+  </si>
+  <si>
+    <t>ok_joint_bracket_5_limit</t>
+  </si>
+  <si>
+    <t>14400</t>
+  </si>
+  <si>
+    <t>OK 2025 Form 511 packet, Income Tax Table: MFJ/HOH/QSS 3.75% to $14,400; 4.75% over</t>
+  </si>
+  <si>
+    <t>ok_joint_high_base</t>
+  </si>
+  <si>
+    <t>4373</t>
+  </si>
+  <si>
+    <t>OK 2025 Form 511 packet, Income Tax Table p.38: MFJ/HOH/QSS $100,000 or more: $4,373 plus 0.0475 over $100,000</t>
+  </si>
+  <si>
+    <t>ok_limit_1</t>
+  </si>
+  <si>
+    <t>ok_limit_2</t>
+  </si>
+  <si>
+    <t>ok_limit_3</t>
+  </si>
+  <si>
+    <t>ok_limit_4</t>
+  </si>
+  <si>
+    <t>ok_limit_5</t>
+  </si>
+  <si>
     <t>ok_military_retirement_exemption</t>
   </si>
   <si>
@@ -270,7 +448,55 @@
     <t>ok_personal_exemption_credit</t>
   </si>
   <si>
-    <t>OK personal exemption credit per exemption (2025). Includes taxpayer, spouse (if MFJ), and dependents. Source: Oklahoma Tax Commission</t>
+    <t>Form 511 line 11: $1,000 for each exemption (an exemption, not a credit)</t>
+  </si>
+  <si>
+    <t>ok_senior_limit</t>
+  </si>
+  <si>
+    <t>ok_senior_limit_hoh</t>
+  </si>
+  <si>
+    <t>19000</t>
+  </si>
+  <si>
+    <t>Form 511 exemptions: extra 65+ exemption only if Federal AGI is $19,000 or less, HOH</t>
+  </si>
+  <si>
+    <t>ok_senior_limit_joint</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>Form 511 exemptions: extra 65+ exemption only if Federal AGI is $25,000 or less, joint</t>
+  </si>
+  <si>
+    <t>ok_senior_limit_mfs</t>
+  </si>
+  <si>
+    <t>12500</t>
+  </si>
+  <si>
+    <t>Form 511 exemptions: extra 65+ exemption only if Federal AGI is $12,500 or less, MFS</t>
+  </si>
+  <si>
+    <t>ok_senior_limit_single</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>Form 511 exemptions: extra 65+ exemption only if Federal AGI (line 1) is $15,000 or less, single</t>
+  </si>
+  <si>
+    <t>ok_single_high_base</t>
+  </si>
+  <si>
+    <t>4562</t>
+  </si>
+  <si>
+    <t>OK 2025 Form 511 packet, Income Tax Table p.38: Single/MFS $100,000 or more: $4,562 plus 0.0475 over $100,000</t>
   </si>
   <si>
     <t>ok_standard_deduction_hoh</t>
@@ -279,7 +505,7 @@
     <t>9350.0</t>
   </si>
   <si>
-    <t>OK standard deduction head of household (2025). Source: Oklahoma Tax Commission</t>
+    <t>Form 511 line 10: Head of Household $9,350</t>
   </si>
   <si>
     <t>ok_standard_deduction_joint</t>
@@ -288,7 +514,7 @@
     <t>12700.0</t>
   </si>
   <si>
-    <t>OK standard deduction married filing jointly (2025). Source: Oklahoma Tax Commission</t>
+    <t>Form 511 line 10: Married Filing Joint or Qualifying Surviving Spouse $12,700</t>
   </si>
   <si>
     <t>ok_standard_deduction_mfs</t>
@@ -297,13 +523,28 @@
     <t>6350.0</t>
   </si>
   <si>
-    <t>OK standard deduction married filing separately (2025). Source: Oklahoma Tax Commission</t>
+    <t>Form 511 line 10: Married Filing Separate $6,350</t>
   </si>
   <si>
     <t>ok_standard_deduction_single</t>
   </si>
   <si>
-    <t>OK standard deduction single (2025). Source: Oklahoma Tax Commission</t>
+    <t>Form 511 line 10: Single $6,350</t>
+  </si>
+  <si>
+    <t>ok_std_deduction</t>
+  </si>
+  <si>
+    <t>ok_table_limit</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>OK 2025 Form 511 packet, Income Tax Table: the table is for taxable income less than $100,000</t>
+  </si>
+  <si>
+    <t>ok_table_tax</t>
   </si>
   <si>
     <t>ok_tax</t>
@@ -911,184 +1152,152 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+    <row r="9">
+      <c r="A9" s="5">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>4</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I11" s="1">
         <v>6</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="1">
-        <v>8</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
         <v>9</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N11" s="1">
         <v>11</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O11" s="1">
         <v>12</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q11" s="1">
         <v>14</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R11" s="1">
         <v>15</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S11" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5">
-        <v>1</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1097,113 +1306,644 @@
         <v>17</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>3</v>
+      </c>
+      <c r="G16" s="4">
+        <v>4</v>
+      </c>
+      <c r="H16" s="4">
+        <v>5</v>
+      </c>
+      <c r="I16" s="4">
+        <v>6</v>
+      </c>
+      <c r="J16" s="4">
+        <v>7</v>
+      </c>
+      <c r="K16" s="4">
+        <v>8</v>
+      </c>
+      <c r="L16" s="4">
+        <v>9</v>
+      </c>
+      <c r="M16" s="4">
+        <v>10</v>
+      </c>
+      <c r="N16" s="4">
+        <v>11</v>
+      </c>
+      <c r="O16" s="4">
         <v>12</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="P16" s="4">
         <v>13</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="4">
+      <c r="Q16" s="4">
+        <v>14</v>
+      </c>
+      <c r="R16" s="4">
+        <v>15</v>
+      </c>
+      <c r="S16" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
         <v>1</v>
       </c>
-      <c r="E15" s="4">
+      <c r="B17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
         <v>2</v>
       </c>
-      <c r="F15" s="4">
+      <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
         <v>3</v>
       </c>
-      <c r="G15" s="4">
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
         <v>4</v>
       </c>
-      <c r="H15" s="4">
+      <c r="B20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
         <v>5</v>
       </c>
-      <c r="I15" s="4">
+      <c r="B21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
         <v>6</v>
       </c>
-      <c r="J15" s="4">
+      <c r="B22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
         <v>7</v>
       </c>
-      <c r="K15" s="4">
-        <v>8</v>
-      </c>
-      <c r="L15" s="4">
-        <v>9</v>
-      </c>
-      <c r="M15" s="4">
-        <v>10</v>
-      </c>
-      <c r="N15" s="4">
-        <v>11</v>
-      </c>
-      <c r="O15" s="4">
-        <v>12</v>
-      </c>
-      <c r="P15" s="4">
-        <v>13</v>
-      </c>
-      <c r="Q15" s="4">
-        <v>14</v>
-      </c>
-      <c r="R15" s="4">
-        <v>15</v>
-      </c>
-      <c r="S15" s="4">
-        <v>16</v>
+      <c r="B23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
+        <v>8</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
@@ -1212,8 +1952,9 @@
     <mergeCell ref="C6:S6"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A16:B16"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1229,7 +1970,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1275,7 +2016,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1298,7 +2039,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1371,11 +2112,11 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -1428,11 +2169,11 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1488,58 +2229,58 @@
         <v>1</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1562,6 +2303,492 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
+        <v>7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
+        <v>3</v>
+      </c>
+      <c r="G14" s="4">
+        <v>4</v>
+      </c>
+      <c r="H14" s="4">
+        <v>5</v>
+      </c>
+      <c r="I14" s="4">
+        <v>6</v>
+      </c>
+      <c r="J14" s="4">
+        <v>7</v>
+      </c>
+      <c r="K14" s="4">
+        <v>8</v>
+      </c>
+      <c r="L14" s="4">
+        <v>9</v>
+      </c>
+      <c r="M14" s="4">
+        <v>10</v>
+      </c>
+      <c r="N14" s="4">
+        <v>11</v>
+      </c>
+      <c r="O14" s="4">
+        <v>12</v>
+      </c>
+      <c r="P14" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>14</v>
+      </c>
+      <c r="R14" s="4">
+        <v>15</v>
+      </c>
+      <c r="S14" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:S8"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A14:B14"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="18"/>
     <col customWidth="true" max="2" min="2" width="25"/>
     <col customWidth="true" max="3" min="3" width="10"/>
@@ -1578,56 +2805,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1643,863 +2870,1806 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M42" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M46" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
